--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4745,8 +4861,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4765,1198 +4885,1276 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">애수의 가을밤 — 민요채보-1/애수의 가을밤.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">애수의 가을밤</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">행</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">뜰</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">위</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">앞</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P4" s="13"/>
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="17"/>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="O5" s="17"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="18"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G6" s="18"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="18"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="13"/>
+      <c r="Q6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="15"/>
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="O7" s="15"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E8" s="17"/>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="17"/>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="17"/>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="O8" s="17"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 無</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="O9" s="17"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C10" s="18"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="G10" s="18"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="18"/>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="18"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">반</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 潢</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="15"/>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="O11" s="15"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">창</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">갑</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">스</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 潢</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="17"/>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="O12" s="17"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 汰</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南
 姑</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">락</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="17"/>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲
 姑</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="17"/>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="P13" s="13"/>
+      <c r="Q13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C14" s="18"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="18"/>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 姑</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="18"/>
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="P14" s="13"/>
+      <c r="Q14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="13"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑⁚</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="15"/>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="15"/>
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="15"/>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="K15" s="15"/>
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="P15" s="13"/>
+      <c r="Q15" s="15"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="13"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O16" s="17"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="13"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="I17" s="17"/>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K17" s="17"/>
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="17"/>
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="O17" s="17"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="I18" s="18"/>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="M18" s="18"/>
+      <c r="N18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
+          </r>
+        </is>
+      </c>
+      <c r="O18" s="18"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -974,13 +974,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|南</t>
+          <t xml:space="preserve">仲|–|南</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 南</t>
         </is>
       </c>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢|仲南</t>
+          <t xml:space="preserve">–|潢|仲南</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢
 仲南</t>
         </is>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -2152,13 +2152,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|―</t>
+          <t xml:space="preserve">·|–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·
-―</t>
+–</t>
         </is>
       </c>
       <c r="I47" s="2"/>
@@ -2259,13 +2259,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―|潢姑</t>
+          <t xml:space="preserve">潢|–|潢姑</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢姑</t>
         </is>
       </c>
@@ -2296,13 +2296,13 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|潢姑</t>
+          <t xml:space="preserve">仲|–|潢姑</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 潢姑</t>
         </is>
       </c>
@@ -2438,13 +2438,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―</t>
+          <t xml:space="preserve">仲|–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2689,13 +2689,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|―</t>
+          <t xml:space="preserve">·|–</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·
-―</t>
+–</t>
         </is>
       </c>
       <c r="I62" s="2"/>
@@ -2979,13 +2979,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―</t>
+          <t xml:space="preserve">仲|–</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3190,13 +3190,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―|南</t>
+          <t xml:space="preserve">仲|–|南</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 南</t>
         </is>
       </c>
@@ -3761,13 +3761,13 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|―</t>
+          <t xml:space="preserve">·|–</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·
-―</t>
+–</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -3952,7 +3952,7 @@
       <c r="F4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―
+–
 潢姑</t>
         </is>
       </c>
@@ -3995,7 +3995,7 @@
       <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 潢姑</t>
         </is>
       </c>
@@ -4049,7 +4049,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢
 仲南</t>
         </is>
@@ -4116,7 +4116,7 @@
       <c r="D8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="E8" s="9"/>
@@ -4165,7 +4165,7 @@
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="G9" s="9"/>
@@ -4201,7 +4201,7 @@
       <c r="C10" s="10"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="10"/>
@@ -4221,7 +4221,7 @@
       <c r="I10" s="10"/>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="10"/>
@@ -4406,7 +4406,7 @@
       <c r="D15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 南</t>
         </is>
       </c>
@@ -4432,7 +4432,7 @@
       <c r="L15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―
+–
 南</t>
         </is>
       </c>
@@ -4445,7 +4445,7 @@
       <c r="B16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·
-―</t>
+–</t>
         </is>
       </c>
       <c r="C16" s="9"/>
@@ -4454,7 +4454,7 @@
       <c r="F16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·
-―</t>
+–</t>
         </is>
       </c>
       <c r="G16" s="9"/>
@@ -4498,7 +4498,7 @@
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·
-―</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="9"/>

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3875,692 +3916,692 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">애수의 가을밤</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無無</t>
         </is>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋黃姑</t>
         </is>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲仲</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="24"/>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢黃</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="24"/>
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="24"/>
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="8"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃仲仲</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –
 潢姑</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南仲南</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="9"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲南</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="25"/>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 潢姑</t>
         </is>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋黃</t>
         </is>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="26"/>
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="25"/>
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="9"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="28"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="27"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="I6" s="27"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢
 仲南</t>
         </is>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="28"/>
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="10"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑潢</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="24"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢南</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="24"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢潢</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="24"/>
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="24"/>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋仲</t>
         </is>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="8"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢黃</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲南</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="25"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 仲南</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="25"/>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="9"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲黃</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="25"/>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="25"/>
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="25"/>
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="25"/>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="9"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="27"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="27"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="27"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="10"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無無</t>
         </is>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲潢</t>
         </is>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無潢</t>
         </is>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="22"/>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="8"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南林</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋仲</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="25"/>
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋仲</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="25"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="9"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲林</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="26"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑林</t>
         </is>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="26"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="9"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="10"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 南</t>
         </is>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="24"/>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="24"/>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="I15" s="24"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲林</t>
         </is>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="K15" s="24"/>
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –
 南</t>
         </is>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="8"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="24"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 –</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 –</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="I16" s="25"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南</t>
         </is>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="9"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="25"/>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="25"/>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 –</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="I17" s="25"/>
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="K17" s="25"/>
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="9"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="27"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="27"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="27"/>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="K18" s="27"/>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="10"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -3895,26 +3895,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
       <c r="N3" s="23"/>
       <c r="O3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
       <c r="N4" s="23"/>
       <c r="O4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       <c r="N5" s="23"/>
       <c r="O5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       <c r="N6" s="23"/>
       <c r="O6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
       <c r="N7" s="23"/>
       <c r="O7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
       <c r="E8" s="25"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="25"/>
@@ -4175,7 +4175,7 @@
       <c r="I8" s="25"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 仲南</t>
         </is>
       </c>
@@ -4189,7 +4189,7 @@
       <c r="N8" s="23"/>
       <c r="O8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4231,11 +4231,11 @@
       <c r="N9" s="23"/>
       <c r="O9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4248,14 +4248,14 @@
       <c r="E10" s="27"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="G10" s="27"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4268,7 +4268,7 @@
       <c r="K10" s="27"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4276,7 +4276,7 @@
       <c r="N10" s="23"/>
       <c r="O10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       <c r="N11" s="23"/>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
       <c r="N12" s="23"/>
       <c r="O12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
       <c r="N13" s="23"/>
       <c r="O13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       <c r="N14" s="23"/>
       <c r="O14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -4481,11 +4481,11 @@
       <c r="N15" s="23"/>
       <c r="O15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 –</t>
         </is>
       </c>
@@ -4494,14 +4494,14 @@
       <c r="E16" s="25"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 –</t>
         </is>
       </c>
       <c r="G16" s="25"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="25"/>
@@ -4516,11 +4516,11 @@
       <c r="N16" s="23"/>
       <c r="O16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C17" s="25"/>
@@ -4532,13 +4532,13 @@
       <c r="E17" s="25"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G17" s="25"/>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 –</t>
         </is>
       </c>
@@ -4558,11 +4558,11 @@
       <c r="N17" s="23"/>
       <c r="O17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4575,14 +4575,14 @@
       <c r="E18" s="27"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="G18" s="27"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4595,7 +4595,7 @@
       <c r="K18" s="27"/>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3942,39 +3965,39 @@
           <t xml:space="preserve">無無無</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋黃姑</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲仲</t>
         </is>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="30"/>
       <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢黃</t>
         </is>
       </c>
-      <c r="I3" s="24"/>
+      <c r="I3" s="30"/>
       <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="30"/>
       <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="M3" s="24"/>
+      <c r="M3" s="30"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="24"/>
+      <c r="O3" s="30"/>
     </row>
     <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
@@ -3983,13 +4006,13 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃仲仲</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -3997,27 +4020,27 @@
 潢姑</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南仲南</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="23"/>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -4026,13 +4049,13 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲南</t>
         </is>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -4040,27 +4063,27 @@
 潢姑</t>
         </is>
       </c>
-      <c r="G5" s="25"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋黃</t>
         </is>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K5" s="25"/>
+      <c r="K5" s="31"/>
       <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="25"/>
+      <c r="M5" s="31"/>
       <c r="N5" s="23"/>
-      <c r="O5" s="25"/>
+      <c r="O5" s="31"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -4069,25 +4092,25 @@
           <t xml:space="preserve">仲南</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
@@ -4095,15 +4118,15 @@
 仲南</t>
         </is>
       </c>
-      <c r="K6" s="28"/>
+      <c r="K6" s="34"/>
       <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="M6" s="27"/>
+      <c r="M6" s="33"/>
       <c r="N6" s="23"/>
-      <c r="O6" s="27"/>
+      <c r="O6" s="33"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -4112,39 +4135,39 @@
           <t xml:space="preserve">姑姑潢</t>
         </is>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢南</t>
         </is>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="30"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="24"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢潢</t>
         </is>
       </c>
-      <c r="I7" s="24"/>
+      <c r="I7" s="30"/>
       <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋仲</t>
         </is>
       </c>
-      <c r="M7" s="24"/>
+      <c r="M7" s="30"/>
       <c r="N7" s="23"/>
-      <c r="O7" s="24"/>
+      <c r="O7" s="30"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -4153,41 +4176,41 @@
           <t xml:space="preserve">姑潢黃</t>
         </is>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲南</t>
         </is>
       </c>
-      <c r="I8" s="25"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲南</t>
         </is>
       </c>
-      <c r="K8" s="25"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南</t>
         </is>
       </c>
-      <c r="M8" s="25"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="25"/>
+      <c r="O8" s="31"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -4196,40 +4219,40 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="25"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲黃</t>
         </is>
       </c>
-      <c r="E9" s="25"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="25"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="31"/>
       <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="25"/>
+      <c r="M9" s="31"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="25"/>
+      <c r="O9" s="31"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
@@ -4239,42 +4262,42 @@
 △</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I10" s="27"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="33"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="27"/>
+      <c r="O10" s="33"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -4283,39 +4306,39 @@
           <t xml:space="preserve">無無無</t>
         </is>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲潢</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無潢</t>
         </is>
       </c>
-      <c r="I11" s="22"/>
+      <c r="I11" s="29"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="M11" s="24"/>
+      <c r="M11" s="30"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
+      <c r="O11" s="30"/>
     </row>
     <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
@@ -4324,39 +4347,39 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南林</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋仲</t>
         </is>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲</t>
         </is>
       </c>
-      <c r="I12" s="25"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋仲</t>
         </is>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="25"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="25"/>
+      <c r="O12" s="31"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -4365,39 +4388,39 @@
           <t xml:space="preserve">無仲</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲林</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑林</t>
         </is>
       </c>
-      <c r="K13" s="26"/>
+      <c r="K13" s="32"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無仲</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="23"/>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
@@ -4406,35 +4429,35 @@
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23"/>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="23"/>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
     </row>
     <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
@@ -4443,7 +4466,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C15" s="24"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -4451,25 +4474,25 @@
 南</t>
         </is>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I15" s="24"/>
+      <c r="I15" s="30"/>
       <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲仲林</t>
         </is>
       </c>
-      <c r="K15" s="24"/>
+      <c r="K15" s="30"/>
       <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -4477,9 +4500,9 @@
 南</t>
         </is>
       </c>
-      <c r="M15" s="24"/>
+      <c r="M15" s="30"/>
       <c r="N15" s="23"/>
-      <c r="O15" s="24"/>
+      <c r="O15" s="30"/>
     </row>
     <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
@@ -4489,32 +4512,32 @@
 –</t>
         </is>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="23"/>
-      <c r="E16" s="25"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I16" s="25"/>
+      <c r="I16" s="31"/>
       <c r="J16" s="23"/>
-      <c r="K16" s="25"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲南</t>
         </is>
       </c>
-      <c r="M16" s="25"/>
+      <c r="M16" s="31"/>
       <c r="N16" s="23"/>
-      <c r="O16" s="25"/>
+      <c r="O16" s="31"/>
     </row>
     <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
@@ -4523,40 +4546,40 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C17" s="25"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="31"/>
       <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="I17" s="25"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K17" s="25"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M17" s="25"/>
+      <c r="M17" s="31"/>
       <c r="N17" s="23"/>
-      <c r="O17" s="25"/>
+      <c r="O17" s="31"/>
     </row>
     <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
@@ -4566,42 +4589,42 @@
 △</t>
         </is>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="27"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I18" s="27"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M18" s="27"/>
+      <c r="M18" s="33"/>
       <c r="N18" s="23"/>
-      <c r="O18" s="27"/>
+      <c r="O18" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -410,7 +410,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無㴌|仲|南^</t>
+          <t xml:space="preserve">無姑|仲|南^</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無㴌
+          <t xml:space="preserve">無姑
 仲
 南^</t>
         </is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無㴌
+          <t xml:space="preserve">無姑
 仲
 南^</t>
         </is>

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -1024,10 +1024,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -593,25 +593,9 @@
 가</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">湳
+    <t xml:space="preserve">㳞湳
 湳
 湳</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">뜰
@@ -640,42 +624,9 @@
 은</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">無南
+仲
+南</t>
   </si>
   <si>
     <t xml:space="preserve">내
@@ -779,34 +730,9 @@
 고</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲姑仲</t>
-    </r>
+    <t xml:space="preserve">無
+–南
+仲姑仲</t>
   </si>
   <si>
     <t xml:space="preserve">보
@@ -814,42 +740,9 @@
 지</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">林</t>
-    </r>
+    <t xml:space="preserve">南潢
+南
+林</t>
   </si>
   <si>
     <t xml:space="preserve">오
@@ -863,34 +756,9 @@
 구</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲姑</t>
-    </r>
+    <t xml:space="preserve">無
+–南
+仲姑</t>
   </si>
   <si>
     <t xml:space="preserve">날
@@ -914,25 +782,9 @@
 짓</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
+    <t xml:space="preserve">南
+–
 –</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">바
@@ -965,17 +817,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -1097,7 +949,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1163,6 +1015,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3121,332 +3025,332 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:M10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="18" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="18" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.95" customHeight="true">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B3" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="21" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B4" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="24" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B5" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B6" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="26"/>
+      <c r="L6" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="13"/>
-    </row>
-    <row r="7" customFormat="false" ht="76" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="M6" s="26"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B7" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="100" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B8" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="24" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B9" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="24" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+      <c r="B10" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="26"/>
+      <c r="D10" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="29"/>
+      <c r="H10" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="26"/>
+      <c r="J10" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="26"/>
+      <c r="L10" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="26" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3456,7 +3360,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/애수의 가을밤.xlsx
+++ b/sheets/민요/검수/애수의 가을밤.xlsx
@@ -3031,22 +3031,22 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="17" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="18" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="17" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="17" width="15.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="18" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.95" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="61.54" customHeight="true">
       <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B3" s="20" t="s">
         <v>97</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B4" s="20" t="s">
         <v>171</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B5" s="22" t="s">
         <v>159</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B6" s="20" t="s">
         <v>94</v>
       </c>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M6" s="26"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B7" s="20" t="s">
         <v>97</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B8" s="20" t="s">
         <v>191</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B9" s="28" t="s">
         <v>201</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="115.86" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="137.39" customHeight="true">
       <c r="B10" s="20" t="s">
         <v>106</v>
       </c>
@@ -3360,7 +3360,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
